--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05D4993-7E77-486B-9795-8B5E1D006164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F16AC4-8452-480A-9211-42AB328753FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="697">
   <si>
     <t>选项</t>
     <phoneticPr fontId="23" type="noConversion"/>
@@ -13404,8 +13404,9 @@
         <f t="shared" ca="1" si="34"/>
         <v>138</v>
       </c>
-      <c r="C271" s="3" t="s">
-        <v>130</v>
+      <c r="C271" s="3" t="str">
+        <f ca="1">A4&amp;"any['光学']"</f>
+        <v>2any['光学']</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>459</v>
@@ -13442,8 +13443,9 @@
         <f t="shared" ref="B272:B275" ca="1" si="35">IF(A272=A271,"",A272)</f>
         <v>139</v>
       </c>
-      <c r="C272" s="3" t="s">
-        <v>130</v>
+      <c r="C272" s="3" t="str">
+        <f ca="1">A4&amp;"any['结构']"</f>
+        <v>2any['结构']</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>460</v>
@@ -13480,8 +13482,9 @@
         <f t="shared" ca="1" si="35"/>
         <v>140</v>
       </c>
-      <c r="C273" s="3" t="s">
-        <v>130</v>
+      <c r="C273" s="3" t="str">
+        <f ca="1">A4&amp;"any['硬件']"</f>
+        <v>2any['硬件']</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>461</v>
@@ -13518,8 +13521,9 @@
         <f t="shared" ca="1" si="35"/>
         <v>141</v>
       </c>
-      <c r="C274" s="3" t="s">
-        <v>130</v>
+      <c r="C274" s="3" t="str">
+        <f ca="1">A4&amp;"any['软件']"</f>
+        <v>2any['软件']</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>462</v>

--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F16AC4-8452-480A-9211-42AB328753FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFB7977-8BCA-492B-90CC-D23682030D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="问题" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="697">
   <si>
     <t>选项</t>
     <phoneticPr fontId="23" type="noConversion"/>
@@ -12438,8 +12438,9 @@
         <f t="shared" ca="1" si="19"/>
         <v>123</v>
       </c>
-      <c r="C245" s="3" t="s">
-        <v>130</v>
+      <c r="C245" s="3" t="str">
+        <f ca="1">A4&amp;"any['硬件']"</f>
+        <v>2any['硬件']</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>450</v>
@@ -12513,8 +12514,9 @@
         <f t="shared" ca="1" si="19"/>
         <v>124</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>130</v>
+      <c r="C247" s="3" t="str">
+        <f ca="1">A4&amp;"any['软件']"</f>
+        <v>2any['软件']</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>114</v>
@@ -12630,8 +12632,9 @@
         <f t="shared" ca="1" si="19"/>
         <v>126</v>
       </c>
-      <c r="C250" s="3" t="s">
-        <v>130</v>
+      <c r="C250" s="3" t="str">
+        <f ca="1">A4&amp;"any['软件']"</f>
+        <v>2any['软件']</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>115</v>

--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0289913A-5554-4C14-B8C5-E1A95381CC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA673299-DC17-4C14-88BB-911FE31EBF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="问题" sheetId="1" r:id="rId1"/>
@@ -5330,8 +5330,8 @@
         <v>8</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f ca="1">A2&amp;"==模组 and "&amp;A12&amp;"any['结构']"</f>
-        <v>1==模组 and 7any['结构']</v>
+        <f ca="1">A8&amp;"==模组 and "&amp;A12&amp;"any['结构']"</f>
+        <v>5==模组 and 7any['结构']</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>781</v>
@@ -5497,8 +5497,8 @@
         <v>11</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f ca="1">A17&amp;"==True or "&amp;A2&amp;"==整机"</f>
-        <v>8==True or 1==整机</v>
+        <f ca="1">A17&amp;"==True or "&amp;A8&amp;"==整机"</f>
+        <v>8==True or 5==整机</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>786</v>
@@ -5540,8 +5540,8 @@
         <v>12</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f ca="1">A2&amp;"==模组 and "&amp;A12&amp;"any['硬件']"</f>
-        <v>1==模组 and 7any['硬件']</v>
+        <f ca="1">A8&amp;"==模组 and "&amp;A12&amp;"any['硬件']"</f>
+        <v>5==模组 and 7any['硬件']</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>683</v>
@@ -12440,8 +12440,8 @@
         <v>110</v>
       </c>
       <c r="C201" s="3" t="str">
-        <f ca="1">A2&amp;"==整机 and "&amp;A18&amp;"any['结构']"</f>
-        <v>1==整机 and 8any['结构']</v>
+        <f ca="1">A8&amp;"==整机 and "&amp;A12&amp;"any['结构']"</f>
+        <v>5==整机 and 7any['结构']</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>801</v>

--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Python\project_file_system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA673299-DC17-4C14-88BB-911FE31EBF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51ADC96-6170-4637-8437-080FB748A7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="问题" sheetId="1" r:id="rId1"/>
